--- a/course_registration_form_templates/041_online_membership_form--course_registration_form_templates.xlsx
+++ b/course_registration_form_templates/041_online_membership_form--course_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your first name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter your last name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Email Address</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your email address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter your phone number</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>emergency_contact_name</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Emergency Contact Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the emergency contact's name</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,197 +660,233 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Relationship with Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select your relationship with the emergency contact</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>student_grade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Student Grade</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select your student grade</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
+          <t>payment_plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Payment Plan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select your payment plan</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emergency_contact_address</t>
+          <t>class_level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>emergency_contact_address</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Class Level</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select your class level</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>student_grade</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>student_grade</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select the start date</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payment_plan</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>payment_plan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select the end date</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>class_level</t>
+          <t>classes_per_week</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>class_level</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Classes per Week</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter the number of classes per week</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>class_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Class Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select the class time</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>student_name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,64 +898,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>classes_per_week</t>
+          <t>parents_name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>classes_per_week</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Parent's Name</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter your parent's name</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>class_time</t>
+          <t>parents_email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>class_time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Parent's Email</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter your parent's email</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>student_name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Medical Condition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select your medical condition</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,38 +979,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>parents_name</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>parents_name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Allergies</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter your allergies</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>parents_email</t>
+          <t>emergency_contact_note</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>parents_email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Emergency Contact Note</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please enter a note about the emergency contact</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -952,20 +1028,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>emergency_contact_phone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Emergency Contact Phone</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please enter the emergency contact's phone number</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -980,108 +1060,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>emergency_contact_email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>allergies</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Emergency Contact Email</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Please enter the emergency contact's email</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>emergency_contact_note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>emergency_contact_note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>emergency_contact_email</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>emergency_contact_email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1090,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1123,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1140,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>relative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Relative</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1174,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_plan_choices</t>
+          <t>student_grade_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1208,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>class_level_choices</t>
+          <t>payment_plan_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>class_time_choices</t>
+          <t>class_level_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1276,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>class_time_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1310,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
